--- a/files/exports/de/financings_31_budgetT.xlsx
+++ b/files/exports/de/financings_31_budgetT.xlsx
@@ -354,14 +354,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="30.800000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="73.7" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="14.3" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.75" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="20.900000000000002" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="64.9" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="51.7" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="23.099999999999998" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="38.5" min="8" max="8" bestFit="1" customWidth="1"/>
@@ -459,7 +459,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46240.77014670239</v>
+        <v>46248.71739555391</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -514,6 +514,186 @@
         <v>2200.0</v>
       </c>
       <c r="P2" s="7" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <v>46248.71739555947</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C3" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1581</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung der budgetierten Einnahmen</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>3842800.0</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>3842800.0</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="7" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>46248.71739556156</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C4" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Sozialdemokratische Partei der Schweiz</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>603</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Ablehnung der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1560</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung der budgetierten Einnahmen</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>366830.0</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>361000.0</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>5830.0</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>46248.717395563144</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C5" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>459</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Überparteiliches Komitee Nein zur Neutralitätsinitiative</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>605</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Ablehnung der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1573</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung der budgetierten Einnahmen</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>1200000.0</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>1200000.0</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P5" s="7" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -531,19 +711,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="21.45" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="31.349999999999998" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="13.2" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="30.800000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
+    <col width="73.7" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="14.3" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.75" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="19.799999999999997" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="29.7" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="64.9" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="51.7" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="23.099999999999998" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="18.15" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="38.5" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="41.25" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="36.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="55.00000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="24.75" min="11" max="11" bestFit="1" customWidth="1"/>
     <col width="56.099999999999994" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="61.05" min="13" max="13" bestFit="1" customWidth="1"/>
@@ -670,6 +850,598 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <v>46248.71739556598</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C2" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>4592</v>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Blocher</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Christoph</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>Herrliberg</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="7" t="n">
+        <v>2000000.0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>46014.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <v>46248.71739556835</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C3" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>4593</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Stiftung für bürgerliche Politik</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Zug</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="7" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>46176.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>46248.717395569685</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C4" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>4594</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Pro Schweiz</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="7" t="n">
+        <v>1300000.0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>46245.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>46248.717395571286</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C5" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>4595</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Emil Frey AG</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="7" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="V5" s="5">
+        <v>46223.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>46248.71739557247</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C6" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>4596</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Schweizerische Volkspartei (SVP)</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="7" t="n">
+        <v>50000.0</v>
+      </c>
+      <c r="V6" s="5">
+        <v>46247.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>46248.717395573556</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C7" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4597</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Blocher</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Christoph</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Herrliberg</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="7" t="n">
+        <v>28665.42</v>
+      </c>
+      <c r="V7" s="5">
+        <v>46232.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>46248.717395574684</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>602</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Annahme der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>4598</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Verein zur Wahrung der Schweizer Neutralität</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Herrliberg</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="7" t="n">
+        <v>133316.58</v>
+      </c>
+      <c r="V8" s="5">
+        <v>45927.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>46248.71739557574</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Wahrung der schweizerischen Neutralität (Neutralitätsinitiative)</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>46292.0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>459</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Überparteiliches Komitee Nein zur Neutralitätsinitiative</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Juristische Person oder Personengesellschaft</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>605</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Ablehnung der Abstimmungsvorlage</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1574</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Offenlegung von Zuwendungen über 15 000 Franken</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>4566</v>
+      </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>economiesuisse Verband der Schweizer Unternehmen</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>Monetär</t>
+        </is>
+      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="7" t="n">
+        <v>1200000.0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>46162.0</v>
+      </c>
+    </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
